--- a/AAII_Financials/Quarterly/CLPHY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CLPHY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="92">
   <si>
     <t>CLPHY</t>
   </si>
@@ -656,24 +656,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -684,103 +684,111 @@
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42551</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42369</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42185</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -823,47 +831,53 @@
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S8" s="3">
         <v>5235800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>4961100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>5347300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>5585000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>5727600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>5935300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>6278700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>5591300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>5258000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>4980400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>5186700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>5118100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>5780100</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -906,47 +920,53 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S9" s="3">
         <v>3422100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>3182800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>3616100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>3911700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>3883100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>3874000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>4155700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>3813200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>3364100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>3272200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>3850000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>3448800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>4337800</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -989,47 +1009,53 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S10" s="3">
         <v>1813700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1778300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1731200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1673300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1844500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>2061300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>2123000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1778200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1894000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1708300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1336700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1669200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1442300</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1059,8 +1085,10 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1142,8 +1170,14 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1225,8 +1259,14 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1299,17 +1339,23 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
         <v>-1133800</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1352,47 +1398,53 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="3">
         <v>557100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>528800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>525300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>510500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>509700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>511500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>488900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>461000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>461500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>429000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>433500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>430300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>452000</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1419,8 +1471,10 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1463,47 +1517,53 @@
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="3">
         <v>4309900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>4001600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>4431700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>5523400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>4676900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>4668900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>4919800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>4539800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>4079300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>3949100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>3377400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>4117500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>5049300</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1546,47 +1606,53 @@
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="3">
         <v>925900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>959500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>915600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>61500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1050700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1266400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1358900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>1051500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>1178700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1031400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>1809300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>1000600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>730800</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1616,8 +1682,10 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1660,47 +1728,53 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="3">
         <v>122800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>186000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>162300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>173000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>144600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>145100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>89700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>54300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>53900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>107400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>104500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>105600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>87900</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1743,47 +1817,53 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3">
         <v>1077700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1674300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1091200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>745000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1194900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1911500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>1476400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1555300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1264000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1556800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>1919000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>1525600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>1253900</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1826,47 +1906,53 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3">
         <v>99600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>108600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>108200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>113300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>112700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>115900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>116800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>100800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>116700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>106900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>289700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>135900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>162200</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1909,47 +1995,53 @@
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="3">
         <v>949100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1036900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>969600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>121300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1082600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1295700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1331700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1005100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>1115900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>1031900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>1624100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>970200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>656500</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1992,47 +2084,53 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="3">
         <v>181400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>202000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>187400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>168200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>238600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>273500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>185900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>172500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>195300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>172700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>288500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>168300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2114,8 +2212,14 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2158,47 +2262,53 @@
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S26" s="3">
         <v>767700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>834900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>782200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-46900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>844000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>1022200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>1145800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>832600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>920600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>859200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>1335600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>801900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>645500</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2241,47 +2351,53 @@
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S27" s="3">
         <v>697400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>770400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>710900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-115600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>778900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>949900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1074400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>762400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>849500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>788800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>1265400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>732500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>576000</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2363,8 +2479,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2407,11 +2529,11 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2446,8 +2568,14 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2529,8 +2657,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2612,8 +2746,14 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2656,47 +2796,53 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S32" s="3">
         <v>-122800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-186000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-162300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-173000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-144600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-145100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-89700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-54300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-53900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-107400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-104500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-105600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-87900</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2739,47 +2885,53 @@
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S33" s="3">
         <v>697400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>770400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>710900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-115600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>778900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>949900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1074400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>762400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>849500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>788800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>1265400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>732500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>576000</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2861,8 +3013,14 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2905,135 +3063,147 @@
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S35" s="3">
         <v>697400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>770400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>710900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-115600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>778900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>949900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1074400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>762400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>849500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>788800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>1265400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>732500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>576000</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42551</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42369</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42185</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3063,8 +3233,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3094,156 +3266,164 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>561200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>561300</v>
+      </c>
+      <c r="F41" s="3">
         <v>501700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>501900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>379900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>383300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>640600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>640500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>375100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>374300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>663400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>661700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>298500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>298000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>545200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1300700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>778200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1063800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>836600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1544700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1083200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1279300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>432900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>602000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>450100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>484000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>531100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>562300</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>286000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>286100</v>
+      </c>
+      <c r="F42" s="3">
         <v>316800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>316900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>336600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>339600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>377300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>377200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>323800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>323000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>365700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>364800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>461600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>460800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>936900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>198500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>269300</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3260,589 +3440,637 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2017600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2018100</v>
+      </c>
+      <c r="F43" s="3">
         <v>1486600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1487200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2202200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2221900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1575800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1575400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2058300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2053700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1529700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1526000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1955200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1951900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1387000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1426700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1827600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1405600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1881200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1575800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1859600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1629100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1781800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1434500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1639100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>1433300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1738500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1690000</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>573600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>573700</v>
+      </c>
+      <c r="F44" s="3">
         <v>477600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>477700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>529000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>533800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>452300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>452200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>509500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>508300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>425900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>424900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>454000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>453300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>474000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>748800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>731100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>700600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>786400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>740300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>767100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>392900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>398300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>330900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>349000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>396200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>481800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>463100</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>184500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>184600</v>
+      </c>
+      <c r="F45" s="3">
         <v>148800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>148800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>247900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>250100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>406600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>406500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>598700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>597400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>460600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>459500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1036100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1034300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1072300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>601200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>427600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>513100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>563400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>661500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>550800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1041600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>653200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>668800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>569500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>524200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>488700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>551800</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3622900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3623800</v>
+      </c>
+      <c r="F46" s="3">
         <v>2934200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2935200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3695600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3728700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3455300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3454400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3865400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>3856700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3447300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3439000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>4205400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>4198100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>4419600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>4276000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>4033900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>3683100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>4067600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>4522300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>4260800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>4342900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>3266100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>3036200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>3007800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>2837600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>3240100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>3267200</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2366200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2366800</v>
+      </c>
+      <c r="F47" s="3">
         <v>2594700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>2595700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>2482400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>2504700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2466000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2465400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2434600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2429100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>2660600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>2654100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>2386500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>2382400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>2558400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>2586400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>2315600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>2390200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>2273200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>2257400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>2430400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>2503600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>1693400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>1669100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>1841700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>1844400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>1988600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>1864600</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22746300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>22752300</v>
+      </c>
+      <c r="F48" s="3">
         <v>22628600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>22636700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>21911100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>22107600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>21720600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>21715200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>21106600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>21058900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>20581400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>20531600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>19864000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>19829800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>19859300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>20041700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>19409000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>19265900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>19023000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>18154700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>17889500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>17829200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>17861800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>34563400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>16981600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>16620600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>16851700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>16727900</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1615900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1616300</v>
+      </c>
+      <c r="F49" s="3">
         <v>1629700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1630300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1598700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1613100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1602200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1601800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1612300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1608600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1645400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1641500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2334600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2330600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2366300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>2632600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>2501400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>2569600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>2585100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>3428100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>3550200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>3747300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>3714700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>7133900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>3656200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>3599700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>3780400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>3984500</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3924,8 +4152,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4007,91 +4241,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>491400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>491600</v>
+      </c>
+      <c r="F52" s="3">
         <v>313700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>313900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>444300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>448300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>340100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>340000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>522900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>521700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>429000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>427900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>662400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>661300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>525400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>456900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>460200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>408000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>376600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1002700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1014800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>969800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>975300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>1750300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>1144700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>1080800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>1557800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>1632600</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4173,91 +4419,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31351800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>31360000</v>
+      </c>
+      <c r="F54" s="3">
         <v>30660500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>30671500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>30634800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>30909500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>30088600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>30081000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>30012200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>29944400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>29321000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>29249900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>29979700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>29928100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>30270200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>29993500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>28720100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>28316800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>28325500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>29365200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>29145500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>29392700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>27511300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>26602000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>26632000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>25983000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>27418500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>27476900</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4287,8 +4545,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4318,506 +4578,544 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>736500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>736700</v>
+      </c>
+      <c r="F57" s="3">
         <v>795000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>795300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1090300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1100100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>881600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>881400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>917400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>915300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>835800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>833800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>772000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>770700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>835300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>778200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>629700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>747500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>728200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>847500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>849000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>913700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>864800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>776400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>735300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>752100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>751600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1053400</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1930600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1931100</v>
+      </c>
+      <c r="F58" s="3">
         <v>1290300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1290800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1769900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1785800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2099500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2099000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1795900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1791900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1710400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1706200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1779100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1776100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1590700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1148100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1187300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1744100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1977200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1724200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1124200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1091400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1056200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>1373900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>1824800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>1680100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>2139500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>1233500</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2813000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2813800</v>
+      </c>
+      <c r="F59" s="3">
         <v>2850000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2851000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2646800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2670500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2787000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2786300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2822000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2815600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2891600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2884600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3030100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3024900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>3276100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>2684400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>2456600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>2678300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>2602400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>2732000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>2571000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>2688700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1956800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>2699100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>2460100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>2445100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>2675300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>2501200</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5480200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5481600</v>
+      </c>
+      <c r="F60" s="3">
         <v>4935300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4937100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5507000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>5556400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>5768100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>5766700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5535300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>5522800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>5437800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>5424600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>5581200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>5571600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>5702100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>4610700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>4273600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>5169800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>5307900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>5303800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>4544200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>4693800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>3877800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>4849400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>5020200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>4877400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>5566500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>4788200</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6746400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6748200</v>
+      </c>
+      <c r="F61" s="3">
         <v>6812200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>6814600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>6744600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>6805100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>6455100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>6453500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>6323600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>6309300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>5884000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>5869800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>6254600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>6243900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>6236600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>5839200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>6071000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>4957200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>4910800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>5320200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>6227100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>6295800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>5904200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>5287900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>5558300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>5387800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>6736800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>7401600</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1423500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1423800</v>
+      </c>
+      <c r="F62" s="3">
         <v>1326700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1327100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1390200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1402700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1257000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1256700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1453100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1449800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1282200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1279000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1303700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1301400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1221200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3412900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>3191400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2943100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2831600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2826100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2738700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2749400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2964000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>2821000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>2761100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>2860000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>2827000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>3004300</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4899,8 +5197,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4982,8 +5286,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5065,91 +5375,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16014500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>16018600</v>
+      </c>
+      <c r="F66" s="3">
         <v>15574000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>15579500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>15902600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>16045200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>15911800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>15907800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>15476700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>15441700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>14934900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>14898700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>15224300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>15198000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>15432500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>15128600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>14786800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>14346100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>14328800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>14735200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>14398000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>14643200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>13656100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>13212700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>13600700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>13383000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>15396400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>15470000</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5179,8 +5501,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5262,8 +5586,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5345,8 +5675,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5428,8 +5764,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5511,91 +5853,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11816000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>11819100</v>
+      </c>
+      <c r="F72" s="3">
         <v>11728700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>11733000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>11384500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>11486600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>11360400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>11357600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>10957800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>10933000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>10780500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>10754400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>10946800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>10928000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>10913900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>11944000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>11674500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>11461200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>11137800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>11831700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>11661300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>11356600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>10684000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>20134000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>9989000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>9648000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>8801200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>8543400</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5677,8 +6031,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5760,8 +6120,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5843,91 +6209,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14579500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>14583300</v>
+      </c>
+      <c r="F76" s="3">
         <v>14323000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>14328100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>13969800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>14095000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>13396200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>13392800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>13757500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>13726400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>13597000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>13564100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>13963100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>13939100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>14028600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>14864900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>13933200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>13970600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>13996700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>14630000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>14747600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>14749500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>13855200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>13389300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>13031200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>12600000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>12022100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>12006900</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6009,96 +6387,108 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42551</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42369</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42185</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6141,47 +6531,53 @@
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S81" s="3">
         <v>697400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>770400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>710900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-115600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>778900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>949900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1074400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>762400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>849500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>788800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>1265400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>732500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>576000</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6211,56 +6607,58 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>300700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>303400</v>
+      </c>
+      <c r="F83" s="3">
         <v>259000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>258900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>291600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>291000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>229600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>229000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>278100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>277600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>223200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>221700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>300700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>301300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>250800</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
@@ -6294,8 +6692,14 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6377,8 +6781,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6460,8 +6870,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6543,8 +6959,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6626,8 +7048,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6709,91 +7137,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>515800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>515900</v>
+      </c>
+      <c r="F89" s="3">
         <v>1052700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1053100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>509000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>513500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>909200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>908900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>577300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>576000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1129400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1126600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>377900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>377200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>994700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>2023200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>842700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1961800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>763300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1855900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1198500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>2310800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>836000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1891000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1161200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1574000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>871900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1930200</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6823,91 +7263,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-468600</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-468700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-501800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-502000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-521400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-526100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-505800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-505600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-498400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-497300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-415700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-414700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-375300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-374700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-525400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-5722000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-5315000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-5792000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-642000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-695200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-622100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-623700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-606000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-498300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-759000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-697500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-718000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-776600</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6989,8 +7437,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7072,91 +7526,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-345300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-345400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-454800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-455000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-461700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-465800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-455000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-454900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-585800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-584500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-364300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-363400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-241200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-240800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-565300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-530500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-761200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-438100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-305100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-923700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-512000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-1696800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-459800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-493800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-575400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>626900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-493400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-855300</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7186,91 +7652,99 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>311100</v>
+      </c>
+      <c r="E96" s="3">
+        <v>311200</v>
+      </c>
+      <c r="F96" s="3">
         <v>204500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>204500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>304100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>306900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>204900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>204800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>297700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>297000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>203700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>203200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>296600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>296100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>204100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-407700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-589400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-406800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-585800</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-392600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-564700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-384000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-547700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-371500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-527100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-354000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-501200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-349300</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7352,8 +7826,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7435,8 +7915,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7518,253 +8004,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-143100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-143100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-541400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-541600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-177900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-179500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-320600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-320600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-131800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-131500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-583800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-582400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-256600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-256100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-440200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-1005600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-302300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-1056100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-850800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-706000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-761700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-182300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-573900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-1233400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-608700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-2203200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-410900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-1386400</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-1800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-2000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-9700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-9700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-10300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-10300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>36200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-11300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-10900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>3100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-19200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-25500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>15700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>15600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-16300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-19400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-14500</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>31600</v>
+      </c>
+      <c r="F102" s="3">
         <v>59300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>59300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-127000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-128100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>131800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>131700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-144300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-143900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>182000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>181500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-122000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-121800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-20500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>523300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-232000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>456600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-389600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>207000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-100800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>447400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-182000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>147600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-31200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-21700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-38500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-325900</v>
       </c>
     </row>
